--- a/examples/list-range-cross-sheet.xlsx
+++ b/examples/list-range-cross-sheet.xlsx
@@ -6,8 +6,8 @@
     <workbookView/>
   </bookViews>
   <sheets>
-    <sheet name="Main" sheetId="1" r:id="rId1"/>
-    <sheet name="Lists" sheetId="2" r:id="rId2"/>
+    <sheet r:id="rId1" sheetId="1" name="Main"/>
+    <sheet r:id="rId2" sheetId="2" name="Lists"/>
   </sheets>
   <definedNames/>
   <calcPr/>
